--- a/Assets/_TankRes/excel/map.xlsx
+++ b/Assets/_TankRes/excel/map.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mapType" sheetId="2" r:id="rId1"/>
+    <sheet name="mapRandom" sheetId="2" r:id="rId1"/>
+    <sheet name="mapNormal" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="58">
   <si>
     <t>唯一标识</t>
   </si>
@@ -99,6 +100,142 @@
   </si>
   <si>
     <t>空格多</t>
+  </si>
+  <si>
+    <t>第1列</t>
+  </si>
+  <si>
+    <t>第2列</t>
+  </si>
+  <si>
+    <t>第3列</t>
+  </si>
+  <si>
+    <t>第4列</t>
+  </si>
+  <si>
+    <t>第5列</t>
+  </si>
+  <si>
+    <t>第6列</t>
+  </si>
+  <si>
+    <t>第7列</t>
+  </si>
+  <si>
+    <t>第8列</t>
+  </si>
+  <si>
+    <t>第9列</t>
+  </si>
+  <si>
+    <t>第10列</t>
+  </si>
+  <si>
+    <t>第11列</t>
+  </si>
+  <si>
+    <t>第12列</t>
+  </si>
+  <si>
+    <t>第13列</t>
+  </si>
+  <si>
+    <t>Y0</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>Y3</t>
+  </si>
+  <si>
+    <t>Y4</t>
+  </si>
+  <si>
+    <t>Y5</t>
+  </si>
+  <si>
+    <t>Y6</t>
+  </si>
+  <si>
+    <t>Y7</t>
+  </si>
+  <si>
+    <t>Y8</t>
+  </si>
+  <si>
+    <t>Y9</t>
+  </si>
+  <si>
+    <t>Y10</t>
+  </si>
+  <si>
+    <t>Y11</t>
+  </si>
+  <si>
+    <t>Y12</t>
+  </si>
+  <si>
+    <t>[int]</t>
+  </si>
+  <si>
+    <t>关卡1
+None = 0,
+Wall=1,
+Stone=2,
+Grass=3,
+Wate=4,
+Snow=5,
+Wall_LU = 10,
+Wall_LD=11,
+Wall_RU=12,
+Wall_RD=13,
+Stone_LU=14,
+Stone_LD=15,
+Stone_RU=16,
+Stone_RD=17,
+Brid=20,
+DeadBrid=21,
+AirBorder=30,</t>
+  </si>
+  <si>
+    <t>10,12</t>
+  </si>
+  <si>
+    <t>11,13</t>
+  </si>
+  <si>
+    <t>14,16</t>
+  </si>
+  <si>
+    <t>12,13</t>
+  </si>
+  <si>
+    <t>10,11</t>
+  </si>
+  <si>
+    <t>关卡2
+None = 0,
+Wall=1,
+Stone=2,
+Grass=3,
+Wate=4,
+Snow=5,
+Wall_LU = 10,
+Wall_LD=11,
+Wall_RU=12,
+Wall_RD=13,
+Stone_LU=14,
+Stone_LD=15,
+Stone_RU=16,
+Stone_RD=17,
+Brid=20,
+DeadBrid=21,
+AirBorder=30,</t>
   </si>
 </sst>
 </file>
@@ -277,7 +414,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,6 +423,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -471,7 +632,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -505,6 +666,17 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -631,7 +803,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -643,55 +815,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
@@ -754,18 +914,51 @@
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1092,52 +1285,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.25" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="31.25" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1355,4 +1548,1337 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="15.0083333333333" customWidth="1"/>
+    <col min="2" max="2" width="27.1666666666667" customWidth="1"/>
+    <col min="3" max="15" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:15">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:15">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:15">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:15">
+      <c r="A5" s="3">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:15">
+      <c r="A6" s="3">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:15">
+      <c r="A7" s="3">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:15">
+      <c r="A8" s="3">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:15">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:15">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:15">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:15">
+      <c r="A12" s="3">
+        <v>5</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:15">
+      <c r="A13" s="3">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:15">
+      <c r="A14" s="3">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>1</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:15">
+      <c r="A15" s="3">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>1</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:15">
+      <c r="A16" s="3">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="6">
+        <v>13</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="6">
+        <v>11</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>1</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:15">
+      <c r="A17" s="3">
+        <v>0</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="8">
+        <v>20</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:15">
+      <c r="A18" s="3">
+        <v>25</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:15">
+      <c r="A19" s="3">
+        <v>24</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:15">
+      <c r="A20" s="3">
+        <v>23</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:15">
+      <c r="A21" s="3">
+        <v>22</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>2</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:15">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:15">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:15">
+      <c r="A24" s="3">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:15">
+      <c r="A25" s="3">
+        <v>18</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:15">
+      <c r="A26" s="3">
+        <v>17</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:15">
+      <c r="A27" s="3">
+        <v>16</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3">
+        <v>2</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:15">
+      <c r="A28" s="3">
+        <v>15</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:15">
+      <c r="A29" s="3">
+        <v>14</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6">
+        <v>13</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" s="6">
+        <v>11</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>1</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>1</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:15">
+      <c r="A30" s="3">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I30" s="8">
+        <v>20</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3">
+        <v>1</v>
+      </c>
+      <c r="N30" s="3">
+        <v>1</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:B17"/>
+    <mergeCell ref="B18:B30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>